--- a/backend/src/test/resources/golden/index_twse_pre_t285.xlsx
+++ b/backend/src/test/resources/golden/index_twse_pre_t285.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>日期</t>
   </si>
@@ -29,9 +29,6 @@
     <t>收盤</t>
   </si>
   <si>
-    <t>週線MA5</t>
-  </si>
-  <si>
     <t>2026-07-30</t>
   </si>
   <si>
@@ -46,7 +43,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -63,17 +60,6 @@
       <name val="Calibri"/>
       <sz val="13.0"/>
       <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="12.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,14 +82,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -114,7 +98,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.73046875" customWidth="true" bestFit="true"/>
@@ -122,7 +106,6 @@
     <col min="3" max="3" width="10.90234375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.90234375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="10.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="7.76953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -141,32 +124,29 @@
       <c r="E1" t="s" s="1">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="1">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
-      <c r="B2" t="n" s="6">
+      <c r="B2" t="n" s="4">
         <v>23000.0</v>
       </c>
-      <c r="C2" t="n" s="6">
+      <c r="C2" t="n" s="4">
         <v>23100.0</v>
       </c>
-      <c r="D2" t="n" s="6">
+      <c r="D2" t="n" s="4">
         <v>22900.0</v>
       </c>
-      <c r="E2" t="n" s="6">
+      <c r="E2" t="n" s="4">
         <v>23050.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
-      <c r="E3" t="n" s="6">
+      <c r="E3" t="n" s="4">
         <v>23200.0</v>
       </c>
     </row>
